--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$14</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -20033,7 +20051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20099,6 +20117,177 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1992_93_0049 'TJ Tesla Žižkov' prev→CLUB_S1991_92_0042 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1992_93_0089 'TJ Slezan Frýdek Místek' prev→CLUB_S1991_92_0078 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1992_93_0203 'Kal. Tábor' prev→CLUB_S1991_92_0189 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1992_93_0219 'Stranná-Žirovnice' prev→CLUB_S1991_92_0211 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1992_93_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1992_93_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1992_93_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1992_93_0033 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1992_93_0034 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1992_93_0035 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0044</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1992_93_0044 'Kvalifikace o 1. ČNHL skupina E' (L30, parent=NODE_S1992_93_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0045</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1992_93_0045 'Kvalifikace o 1. ČNHL skupina F' (L30, parent=NODE_S1992_93_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0047</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1992_93_0047 'O postup do I.ČNHL' (L25, parent=NODE_S1992_93_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -25132,9 +25321,6 @@
         </is>
       </c>
     </row>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
@@ -54587,6 +54773,347 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0049</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0049 'TJ Tesla Žižkov' prev→CLUB_S1991_92_0042 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0089</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0089 'TJ Slezan Frýdek Místek' prev→CLUB_S1991_92_0078 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0203</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0203 'Kal. Tábor' prev→CLUB_S1991_92_0189 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0219</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0219 'Stranná-Žirovnice' prev→CLUB_S1991_92_0211 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0029</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0031</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0032</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0033</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0033 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0034</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0034 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0035</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0035 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0044</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1992_93_0044 'Kvalifikace o 1. ČNHL skupina E' (L30, parent=NODE_S1992_93_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0045</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1992_93_0045 'Kvalifikace o 1. ČNHL skupina F' (L30, parent=NODE_S1992_93_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0047</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1992_93_0047 'O postup do I.ČNHL' (L25, parent=NODE_S1992_93_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20051,7 +20051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20123,7 +20123,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1992_93_0049 'TJ Tesla Žižkov' prev→CLUB_S1991_92_0042 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20135,7 +20135,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1992_93_0089 'TJ Slezan Frýdek Místek' prev→CLUB_S1991_92_0078 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20147,7 +20147,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1992_93_0203 'Kal. Tábor' prev→CLUB_S1991_92_0189 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20159,7 +20159,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1992_93_0219 'Stranná-Žirovnice' prev→CLUB_S1991_92_0211 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20171,7 +20171,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1992_93_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20183,7 +20183,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1992_93_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20195,7 +20195,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1992_93_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20207,7 +20207,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1992_93_0033 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20219,7 +20219,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1992_93_0034 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20231,7 +20231,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1992_93_0035 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20241,14 +20241,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NODE_S1992_93_0044</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1992_93_0044 'Kvalifikace o 1. ČNHL skupina E' (L30, parent=NODE_S1992_93_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20258,14 +20253,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NODE_S1992_93_0045</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1992_93_0045 'Kvalifikace o 1. ČNHL skupina F' (L30, parent=NODE_S1992_93_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20275,17 +20265,372 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NODE_S1992_93_0047</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1992_93_0047 'O postup do I.ČNHL' (L25, parent=NODE_S1992_93_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0042 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0078 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0479 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0189 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0211 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -25321,6 +25666,9 @@
         </is>
       </c>
     </row>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
@@ -28130,12 +28478,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -28597,12 +28945,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -28686,12 +29034,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -28728,12 +29076,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -28812,12 +29160,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -29111,12 +29459,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -29153,12 +29501,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -29269,12 +29617,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -29437,12 +29785,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -29563,12 +29911,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -29689,12 +30037,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -29731,12 +30079,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -29946,12 +30294,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Kežmarok = HK 31 Kežmarok (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj. **HK 31** = nova post-revolucni znacka klubu. city Kežmarok.</t>
+          <t>Kežmarok = HK 31 Kežmarok (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj. **HK 31** = nova post-revolucni znacka klubu. city Kežmarok. || TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>HK 31 Kežmarok</t>
+          <t>Kežmarok</t>
         </is>
       </c>
     </row>
@@ -30581,12 +30929,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -31137,12 +31485,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -31226,12 +31574,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -31441,12 +31789,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -31525,12 +31873,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Piešťany = HK Chirana Piešťany (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj. city Piešťany.</t>
+          <t>Piešťany = HK Chirana Piešťany (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj. city Piešťany. || TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>HK Chirana Piešťany</t>
+          <t>Chirana Piešťany</t>
         </is>
       </c>
     </row>
@@ -35965,12 +36313,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -36054,12 +36402,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -36694,12 +37042,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -37060,12 +37408,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38563,12 +38911,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -40358,12 +40706,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -40573,12 +40921,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -40615,12 +40963,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -40978,12 +41326,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -41497,12 +41845,12 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -42463,12 +42811,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -44198,12 +44546,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -48438,12 +48786,12 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -54779,11 +55127,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -54828,21 +55176,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0049</t>
+          <t>CLUB_S1992_93_0005</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0049 'TJ Tesla Žižkov' prev→CLUB_S1991_92_0042 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -54850,21 +55196,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0089</t>
+          <t>CLUB_S1992_93_0016</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0089 'TJ Slezan Frýdek Místek' prev→CLUB_S1991_92_0078 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -54872,21 +55216,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0203</t>
+          <t>CLUB_S1992_93_0018</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0203 'Kal. Tábor' prev→CLUB_S1991_92_0189 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -54894,21 +55236,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0219</t>
+          <t>CLUB_S1992_93_0019</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0219 'Stranná-Žirovnice' prev→CLUB_S1991_92_0211 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -54916,21 +55256,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0029</t>
+          <t>CLUB_S1992_93_0021</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -54938,21 +55276,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0031</t>
+          <t>CLUB_S1992_93_0028</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -54960,21 +55296,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0032</t>
+          <t>CLUB_S1992_93_0029</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -54982,21 +55316,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0033</t>
+          <t>CLUB_S1992_93_0032</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0033 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -55004,21 +55336,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0034</t>
+          <t>CLUB_S1992_93_0036</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0034 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -55026,21 +55356,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0035</t>
+          <t>CLUB_S1992_93_0039</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0035 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -55048,21 +55376,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NODE_S1992_93_0044</t>
+          <t>CLUB_S1992_93_0042</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1992_93_0044 'Kvalifikace o 1. ČNHL skupina E' (L30, parent=NODE_S1992_93_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -55070,21 +55396,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NODE_S1992_93_0045</t>
+          <t>CLUB_S1992_93_0043</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1992_93_0045 'Kvalifikace o 1. ČNHL skupina F' (L30, parent=NODE_S1992_93_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -55092,24 +55416,622 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NODE_S1992_93_0047</t>
+          <t>CLUB_S1992_93_0048</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1992_93_0047 'O postup do I.ČNHL' (L25, parent=NODE_S1992_93_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0049</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0042 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0063</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0066</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0082</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0084</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0089</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0078 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0090</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0092</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0106</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0479 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0193</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0193</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0195</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0203</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0189 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0210</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0218</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0219</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0211 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0253</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0294</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0299</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0300</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0306</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0309</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0322</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0325</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0331</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0345</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0373</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0386</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0393</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1992_93_0484</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20051,7 +20051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20123,7 +20123,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20135,7 +20135,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20147,7 +20147,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20159,7 +20159,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20171,7 +20171,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20183,7 +20183,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20195,7 +20195,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20207,7 +20207,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20219,7 +20219,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0042 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20231,7 +20231,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20243,7 +20243,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20255,7 +20255,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20267,7 +20267,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20279,7 +20279,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0042 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0078 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -20291,7 +20291,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20303,7 +20303,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -20315,7 +20315,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0479 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20327,7 +20327,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: D44 můstek prev_club_id → CLUB_S1991_92_0119 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -20339,7 +20339,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0078 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -20351,7 +20351,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0189 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -20363,7 +20363,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -20375,7 +20375,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0479 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -20387,7 +20387,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0211 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -20399,7 +20399,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -20411,7 +20411,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -20423,7 +20423,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0189 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -20435,7 +20435,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -20447,7 +20447,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -20459,7 +20459,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0211 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -20471,7 +20471,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -20483,7 +20483,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20495,7 +20495,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -20507,7 +20507,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20519,7 +20519,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20531,106 +20531,10 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -20647,7 +20551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:L125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20706,6 +20610,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20748,6 +20657,11 @@
           <t>14 týmů: základ + playoff (8F/QF/SF/finále/O 3.). Mistr: Sparta Praha.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20837,6 +20751,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20879,6 +20798,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20921,6 +20845,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20963,6 +20892,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21005,6 +20939,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21047,6 +20986,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21089,6 +21033,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21131,6 +21080,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21173,6 +21127,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21215,6 +21174,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21257,6 +21221,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21299,6 +21268,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21341,6 +21315,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21383,6 +21362,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21425,6 +21409,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21467,6 +21456,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -21509,6 +21503,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -21551,6 +21550,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -21598,6 +21602,11 @@
           <t>AC Nitra – Motor České Budějovice 1:3. Nitra hrála jen tuto kvalifikaci; 1. a 3. utkání doma, případné 5. v Olomouci.</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0002</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21640,6 +21649,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -21682,6 +21696,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -21724,6 +21743,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -21771,6 +21795,11 @@
           <t>Finálová skupina. Dne 12.12.1992 byl změněn formát play-off a určení postupu do nové Extraligy.</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -21860,6 +21889,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -21907,6 +21941,11 @@
           <t>Skupina o 9.-14. místo.</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -21996,6 +22035,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -22122,6 +22166,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -22164,6 +22213,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -22248,6 +22302,11 @@
           <t>II.ČNHL: 3 skupiny + finále.</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0036</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -22290,6 +22349,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0037</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -22332,6 +22396,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0038</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -22374,6 +22443,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0039</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22416,6 +22490,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0040</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -22458,6 +22537,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0041</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -22500,6 +22584,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0042</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -22542,6 +22631,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0043</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -22678,6 +22772,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0047</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -22720,6 +22819,11 @@
           <t>II.SNHL: skupina západ, střed, východ; finálová skupina; skupiny o umístění západ/střed/východ.</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0048</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -22762,6 +22866,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0049</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -22804,6 +22913,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0050</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -22846,6 +22960,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0051</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -22888,6 +23007,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0052</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -22930,6 +23054,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0053</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -22972,6 +23101,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0054</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -23056,6 +23190,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0058</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -23098,6 +23237,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0059</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -23140,6 +23284,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0060</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -23182,6 +23331,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0061</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -23224,6 +23378,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0062</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -23434,6 +23593,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0064</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -23476,6 +23640,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0065</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -23560,6 +23729,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0066</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -23602,6 +23776,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0067</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -23644,6 +23823,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0068</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -23686,6 +23870,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0069</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -23728,6 +23917,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0070</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -23770,6 +23964,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0071</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -23812,6 +24011,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0072</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -23943,6 +24147,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0076</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -23985,6 +24194,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0077</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24027,6 +24241,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0078</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24069,6 +24288,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0079</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -24111,6 +24335,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0080</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -24615,6 +24844,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0087</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -24657,6 +24891,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0088</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -24741,6 +24980,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0089</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -24783,6 +25027,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0090</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -24993,6 +25242,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0097</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -25035,6 +25289,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0098</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -25077,6 +25336,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0102</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -25119,6 +25383,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0103</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -25371,6 +25640,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0108</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -25413,6 +25687,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0109</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -25453,6 +25732,11 @@
       <c r="J113" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>NODE_S1991_92_0110</t>
         </is>
       </c>
     </row>
@@ -28478,12 +28762,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -28945,12 +29229,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -29160,12 +29444,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -29459,12 +29743,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -30079,12 +30363,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -33220,9 +33504,14 @@
           <t>L40</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0119</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Mělník = TJ Dukla Mělník (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **VTJ Dukla Mělník** = vojenska telovychovna jednota. Patterns: Sokol Mělník -&gt; Dukla Mělník -&gt; VTJ Dukla Mělník. city Mělník.</t>
+          <t>Mělník = TJ Dukla Mělník (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **VTJ Dukla Mělník** = vojenska telovychovna jednota. Patterns: Sokol Mělník -&gt; Dukla Mělník -&gt; VTJ Dukla Mělník. city Mělník. || TBD: D44 můstek prev_club_id → CLUB_S1991_92_0119 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -36313,12 +36602,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -36402,12 +36691,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -42811,12 +43100,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -48786,12 +49075,12 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -55127,7 +55416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -55181,12 +55470,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0005</t>
+          <t>CLUB_S1992_93_0018</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55201,12 +55490,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0016</t>
+          <t>CLUB_S1992_93_0019</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55221,12 +55510,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0018</t>
+          <t>CLUB_S1992_93_0029</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55241,12 +55530,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0019</t>
+          <t>CLUB_S1992_93_0032</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55261,12 +55550,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0021</t>
+          <t>CLUB_S1992_93_0036</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55281,12 +55570,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0028</t>
+          <t>CLUB_S1992_93_0039</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55301,12 +55590,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0029</t>
+          <t>CLUB_S1992_93_0042</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55321,12 +55610,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0032</t>
+          <t>CLUB_S1992_93_0048</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55341,12 +55630,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0036</t>
+          <t>CLUB_S1992_93_0049</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0042 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55361,12 +55650,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0039</t>
+          <t>CLUB_S1992_93_0063</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -55381,12 +55670,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0042</t>
+          <t>CLUB_S1992_93_0066</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55401,12 +55690,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0043</t>
+          <t>CLUB_S1992_93_0082</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55421,12 +55710,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0048</t>
+          <t>CLUB_S1992_93_0084</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55441,12 +55730,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0049</t>
+          <t>CLUB_S1992_93_0089</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0042 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0078 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55461,12 +55750,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0063</t>
+          <t>CLUB_S1992_93_0090</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55481,12 +55770,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0066</t>
+          <t>CLUB_S1992_93_0092</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55501,12 +55790,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0082</t>
+          <t>CLUB_S1992_93_0106</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0479 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55521,12 +55810,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0084</t>
+          <t>CLUB_S1992_93_0124</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: D44 můstek prev_club_id → CLUB_S1991_92_0119 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
     </row>
@@ -55541,12 +55830,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0089</t>
+          <t>CLUB_S1992_93_0193</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0078 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55561,12 +55850,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0090</t>
+          <t>CLUB_S1992_93_0203</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0189 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55581,12 +55870,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0092</t>
+          <t>CLUB_S1992_93_0210</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55601,12 +55890,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0106</t>
+          <t>CLUB_S1992_93_0218</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0479 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55621,12 +55910,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0193</t>
+          <t>CLUB_S1992_93_0219</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0211 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -55641,12 +55930,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0193</t>
+          <t>CLUB_S1992_93_0253</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55661,12 +55950,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0195</t>
+          <t>CLUB_S1992_93_0294</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55681,12 +55970,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0203</t>
+          <t>CLUB_S1992_93_0299</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0189 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55701,12 +55990,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0210</t>
+          <t>CLUB_S1992_93_0300</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55721,12 +56010,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0218</t>
+          <t>CLUB_S1992_93_0306</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -55741,12 +56030,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0219</t>
+          <t>CLUB_S1992_93_0309</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0211 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55761,12 +56050,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0253</t>
+          <t>CLUB_S1992_93_0322</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55781,12 +56070,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0294</t>
+          <t>CLUB_S1992_93_0325</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -55801,12 +56090,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0299</t>
+          <t>CLUB_S1992_93_0331</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -55821,12 +56110,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0300</t>
+          <t>CLUB_S1992_93_0373</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -55841,12 +56130,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0306</t>
+          <t>CLUB_S1992_93_0386</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -55861,177 +56150,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1992_93_0309</t>
+          <t>CLUB_S1992_93_0393</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1992_93_0322</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1992_93_0325</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1992_93_0331</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1992_93_0345</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1992_93_0373</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1992_93_0386</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1992_93_0393</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
           <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1992_93_0484</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F44"/>
+  <autoFilter ref="A1:F36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -66906,6 +67035,11 @@
           <t>CLUB_S1992_93_0124</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0119</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>setrval?</t>
@@ -67584,6 +67718,11 @@
       <c r="Q39" t="inlineStr">
         <is>
           <t>CLUB_S1992_93_0124</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>CLUB_S1991_92_0119</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">

--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -19507,7 +19507,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / do 2. ligy nepostoupil žádný zájemce</t>
+          <t>Krajský přebor</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -19733,7 +19733,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / do 2. ligy nepostoupil žádný zájemce</t>
+          <t>Krajský přebor</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -20051,7 +20051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20121,33 +20121,43 @@
       </c>
     </row>
     <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30ZASL</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] do 2. ligy nepostoupil žádný zájemce</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30STSL</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] do 2. ligy nepostoupil žádný zájemce</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20159,7 +20169,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20171,7 +20181,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20183,7 +20193,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20195,7 +20205,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20207,7 +20217,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20219,7 +20229,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0042 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20231,7 +20241,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20243,7 +20253,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0042 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20255,7 +20265,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20267,7 +20277,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20279,7 +20289,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0078 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -20291,7 +20301,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20303,7 +20313,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0078 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -20315,7 +20325,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0479 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20327,7 +20337,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: D44 můstek prev_club_id → CLUB_S1991_92_0119 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -20339,7 +20349,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0479 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -20351,7 +20361,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0189 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: D44 můstek prev_club_id → CLUB_S1991_92_0119 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -20363,7 +20373,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -20375,7 +20385,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0189 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -20387,7 +20397,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0211 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -20399,7 +20409,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -20411,7 +20421,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0211 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -20423,7 +20433,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -20435,7 +20445,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -20447,7 +20457,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -20459,7 +20469,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -20471,7 +20481,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -20483,7 +20493,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20495,7 +20505,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -20507,7 +20517,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20519,7 +20529,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20531,10 +20541,34 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>

--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20051,7 +20051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20569,6 +20569,90 @@
         </is>
       </c>
       <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -55450,7 +55534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -56193,8 +56277,148 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HC Vítkovice</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HC Košice</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AC ZPS Zlín</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HC Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HC Pardubice</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HC Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F36"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -760,16 +760,16 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -777,7 +777,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>168</v>
+        <v>126</v>
+      </c>
+      <c r="M5" t="n">
+        <v>53</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -838,13 +841,13 @@
         <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -852,7 +855,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>150</v>
+        <v>108</v>
+      </c>
+      <c r="M6" t="n">
+        <v>53</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -913,13 +919,13 @@
         <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -927,7 +933,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>167</v>
+        <v>148</v>
+      </c>
+      <c r="M7" t="n">
+        <v>46</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -988,13 +997,13 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1002,7 +1011,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>174</v>
+        <v>147</v>
+      </c>
+      <c r="M8" t="n">
+        <v>44</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1065,16 +1077,16 @@
         <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1082,7 +1094,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>142</v>
+        <v>122</v>
+      </c>
+      <c r="M9" t="n">
+        <v>44</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1140,16 +1155,16 @@
         <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1157,7 +1172,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>135</v>
+        <v>142</v>
+      </c>
+      <c r="M10" t="n">
+        <v>43</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1218,13 +1236,13 @@
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1232,7 +1250,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>137</v>
+        <v>140</v>
+      </c>
+      <c r="M11" t="n">
+        <v>41</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1293,13 +1314,13 @@
         <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1307,7 +1328,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>126</v>
+        <v>120</v>
+      </c>
+      <c r="M12" t="n">
+        <v>39</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1365,16 +1389,16 @@
         <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1382,7 +1406,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>137</v>
+        <v>143</v>
+      </c>
+      <c r="M13" t="n">
+        <v>38</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1443,13 +1470,13 @@
         <v>16</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1457,7 +1484,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>131</v>
+        <v>150</v>
+      </c>
+      <c r="M14" t="n">
+        <v>36</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1518,13 +1548,13 @@
         <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1532,7 +1562,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>124</v>
+        <v>149</v>
+      </c>
+      <c r="M15" t="n">
+        <v>35</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1590,16 +1623,16 @@
         <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
         <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1640,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>123</v>
+        <v>161</v>
+      </c>
+      <c r="M16" t="n">
+        <v>31</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1665,16 +1701,16 @@
         <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1682,7 +1718,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>115</v>
+        <v>145</v>
+      </c>
+      <c r="M17" t="n">
+        <v>31</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1743,13 +1782,13 @@
         <v>12</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1757,7 +1796,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>125</v>
+        <v>153</v>
+      </c>
+      <c r="M18" t="n">
+        <v>26</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -20051,7 +20093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20569,90 +20611,6 @@
         </is>
       </c>
       <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -55534,7 +55492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -56277,148 +56235,8 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>HC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>HC Vítkovice</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>HC Košice</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AC ZPS Zlín</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>HC Dukla Jihlava</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>HC Pardubice</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>HC Slovan Bratislava</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>vstřelené branky (GF) = 0/chybí — ověřit ze zdroje</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -52321,7 +52321,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M25" t="n">
         <v>7</v>

--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -20627,7 +20627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L125"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20691,6 +20691,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26026,9 +26036,6 @@
         </is>
       </c>
     </row>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>

--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -20968,6 +20968,16 @@
           <t>NODE_S1992_93_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0011</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0017</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20982,6 +20992,14 @@
         <is>
           <t>NODE_S1991_92_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -21156,6 +21174,16 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0020</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21170,6 +21198,14 @@
         <is>
           <t>NODE_S1991_92_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -21203,6 +21239,16 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0012</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0020</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21217,6 +21263,14 @@
         <is>
           <t>NODE_S1991_92_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -21250,6 +21304,16 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0016</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0015</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21264,6 +21328,14 @@
         <is>
           <t>NODE_S1991_92_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -21297,6 +21369,8 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21311,6 +21385,14 @@
         <is>
           <t>NODE_S1991_92_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -21344,6 +21426,8 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21358,6 +21442,14 @@
         <is>
           <t>NODE_S1991_92_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -21391,6 +21483,8 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21405,6 +21499,14 @@
         <is>
           <t>NODE_S1991_92_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -21438,6 +21540,8 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21452,6 +21556,14 @@
         <is>
           <t>NODE_S1991_92_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -21485,6 +21597,8 @@
           <t>NODE_S1992_93_0001</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21499,6 +21613,14 @@
         <is>
           <t>NODE_S1991_92_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -21532,6 +21654,8 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21546,6 +21670,14 @@
         <is>
           <t>NODE_S1991_92_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -21579,6 +21711,8 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21593,6 +21727,14 @@
         <is>
           <t>NODE_S1991_92_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -21626,6 +21768,16 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0014</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0013</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21640,6 +21792,14 @@
         <is>
           <t>NODE_S1991_92_0020</t>
         </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -21725,6 +21885,12 @@
           <t>NODE_S1992_93_0004</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21739,6 +21905,14 @@
         <is>
           <t>NODE_S1991_92_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -21772,6 +21946,16 @@
           <t>NODE_S1992_93_0004</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21786,6 +21970,14 @@
         <is>
           <t>NODE_S1991_92_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -21819,6 +22011,8 @@
           <t>NODE_S1992_93_0004</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21833,6 +22027,14 @@
         <is>
           <t>NODE_S1991_92_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -21918,6 +22120,8 @@
           <t>NODE_S1992_93_0004</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21932,6 +22136,14 @@
         <is>
           <t>Série o 5. místo.</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -21965,6 +22177,12 @@
           <t>NODE_S1992_93_0004</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0026</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21979,6 +22197,14 @@
         <is>
           <t>NODE_S1991_92_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -22012,6 +22238,8 @@
           <t>NODE_S1992_93_0004</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22031,6 +22259,14 @@
         <is>
           <t>NODE_S1991_92_0028</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -22242,6 +22478,12 @@
           <t>NODE_S1992_93_0030</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0034</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22256,6 +22498,14 @@
         <is>
           <t>NODE_S1991_92_0033</t>
         </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -22289,6 +22539,8 @@
           <t>NODE_S1992_93_0030</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22303,6 +22555,14 @@
         <is>
           <t>NODE_S1991_92_0034</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -22613,6 +22873,12 @@
           <t>NODE_S1992_93_0036</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0043</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22627,6 +22893,14 @@
         <is>
           <t>NODE_S1991_92_0041</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -22660,6 +22934,12 @@
           <t>NODE_S1992_93_0036</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0043</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22674,6 +22954,14 @@
         <is>
           <t>NODE_S1991_92_0042</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -22707,6 +22995,8 @@
           <t>NODE_S1992_93_0036</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22721,6 +23011,14 @@
         <is>
           <t>NODE_S1991_92_0043</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -23083,6 +23381,8 @@
           <t>NODE_S1992_93_0048</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23097,6 +23397,14 @@
         <is>
           <t>NODE_S1991_92_0052</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -23130,6 +23438,8 @@
           <t>NODE_S1992_93_0048</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23144,6 +23454,14 @@
         <is>
           <t>NODE_S1991_92_0053</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -23177,6 +23495,8 @@
           <t>NODE_S1992_93_0048</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23191,6 +23511,14 @@
         <is>
           <t>NODE_S1991_92_0054</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -23360,6 +23688,16 @@
           <t>NODE_S1992_93_0058</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0061</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0062</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23374,6 +23712,14 @@
         <is>
           <t>NODE_S1991_92_0060</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -23407,6 +23753,8 @@
           <t>NODE_S1992_93_0058</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23421,6 +23769,14 @@
         <is>
           <t>NODE_S1991_92_0061</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -23454,6 +23810,8 @@
           <t>NODE_S1992_93_0058</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23468,6 +23826,14 @@
         <is>
           <t>NODE_S1991_92_0062</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -23543,6 +23909,16 @@
           <t>NODE_S1992_93_0058</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0061</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0062</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23552,6 +23928,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -23585,6 +23969,8 @@
           <t>NODE_S1992_93_0058</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23594,6 +23980,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -23627,6 +24021,8 @@
           <t>NODE_S1992_93_0058</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23636,6 +24032,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -24134,6 +24538,8 @@
           <t>NODE_S1992_93_0073</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24143,6 +24549,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -24176,6 +24590,8 @@
           <t>NODE_S1992_93_0073</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24185,6 +24601,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -24458,6 +24882,12 @@
           <t>NODE_S1992_93_0082</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0092</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24467,6 +24897,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -24542,6 +24980,8 @@
           <t>NODE_S1992_93_0082</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24551,6 +24991,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -24794,6 +25242,16 @@
           <t>NODE_S1992_93_0082</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0094</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0093</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24803,6 +25261,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -24836,6 +25302,8 @@
           <t>NODE_S1992_93_0082</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24845,6 +25313,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -24878,6 +25354,8 @@
           <t>NODE_S1992_93_0082</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24887,6 +25365,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -25150,6 +25636,16 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0102</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0101</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25159,6 +25655,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="99">
@@ -25192,6 +25696,8 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25201,6 +25707,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -25234,6 +25748,8 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25243,6 +25759,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -25590,6 +26114,8 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25599,6 +26125,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -25632,6 +26166,8 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25641,6 +26177,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -25674,6 +26218,8 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25683,6 +26229,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -25711,6 +26265,12 @@
           <t>REG_SVM</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>NODE_S1992_93_0118</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25730,6 +26290,14 @@
         <is>
           <t>NODE_S1991_92_0108</t>
         </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -25941,6 +26509,8 @@
           <t>NODE_S1992_93_0113</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25950,6 +26520,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="117">
@@ -25983,6 +26561,8 @@
           <t>NODE_S1992_93_0113</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25992,6 +26572,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -26025,6 +26613,8 @@
           <t>NODE_S1992_93_0113</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26035,7 +26625,18 @@
           <t>complete</t>
         </is>
       </c>
-    </row>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>

--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -834,6 +834,11 @@
           <t>HC Sparta Praha</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>40</v>
       </c>
@@ -20093,7 +20098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20613,6 +20618,13 @@
       <c r="D40" t="inlineStr">
         <is>
           <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1992/93 (poslední federální liga): mistr HC Sparta Praha — ve finále play-off porazila Vítkovice 3:1. Litvínov byl 1. ZČ, ale vypadl v semifinále. Doloženo webem.</t>
         </is>
       </c>
     </row>
@@ -21369,8 +21381,6 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21426,8 +21436,6 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21483,8 +21491,6 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21540,8 +21546,6 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21597,8 +21601,6 @@
           <t>NODE_S1992_93_0001</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21654,8 +21656,6 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21711,8 +21711,6 @@
           <t>NODE_S1992_93_0009</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21890,7 +21888,6 @@
           <t>NODE_S1992_93_0023</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22011,8 +22008,6 @@
           <t>NODE_S1992_93_0004</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22120,8 +22115,6 @@
           <t>NODE_S1992_93_0004</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22182,7 +22175,6 @@
           <t>NODE_S1992_93_0026</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22238,8 +22230,6 @@
           <t>NODE_S1992_93_0004</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22483,7 +22473,6 @@
           <t>NODE_S1992_93_0034</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22539,8 +22528,6 @@
           <t>NODE_S1992_93_0030</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22878,7 +22865,6 @@
           <t>NODE_S1992_93_0043</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22939,7 +22925,6 @@
           <t>NODE_S1992_93_0043</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22995,8 +22980,6 @@
           <t>NODE_S1992_93_0036</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23381,8 +23364,6 @@
           <t>NODE_S1992_93_0048</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23438,8 +23419,6 @@
           <t>NODE_S1992_93_0048</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23495,8 +23474,6 @@
           <t>NODE_S1992_93_0048</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23753,8 +23730,6 @@
           <t>NODE_S1992_93_0058</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23810,8 +23785,6 @@
           <t>NODE_S1992_93_0058</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23969,8 +23942,6 @@
           <t>NODE_S1992_93_0058</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24021,8 +23992,6 @@
           <t>NODE_S1992_93_0058</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24538,8 +24507,6 @@
           <t>NODE_S1992_93_0073</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24590,8 +24557,6 @@
           <t>NODE_S1992_93_0073</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24887,7 +24852,6 @@
           <t>NODE_S1992_93_0092</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24980,8 +24944,6 @@
           <t>NODE_S1992_93_0082</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25302,8 +25264,6 @@
           <t>NODE_S1992_93_0082</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25354,8 +25314,6 @@
           <t>NODE_S1992_93_0082</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25696,8 +25654,6 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25748,8 +25704,6 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26114,8 +26068,6 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26166,8 +26118,6 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26218,8 +26168,6 @@
           <t>NODE_S1992_93_0096</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26270,7 +26218,6 @@
           <t>NODE_S1992_93_0118</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26509,8 +26456,6 @@
           <t>NODE_S1992_93_0113</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26561,8 +26506,6 @@
           <t>NODE_S1992_93_0113</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26613,8 +26556,6 @@
           <t>NODE_S1992_93_0113</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26634,9 +26575,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
@@ -55858,7 +55796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56086,6 +56024,18 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>Po sezóně odstoupily Nové Zámky a Gelnica; rezerva Michalovců přešla do Brezna a sloučila se s Mostárnou; z krajů měl zájem jen TJ Baník Rožňava.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HC Sparta Praha</t>
         </is>
       </c>
     </row>

--- a/data/S1992_93_FINAL.xlsx
+++ b/data/S1992_93_FINAL.xlsx
@@ -20202,21 +20202,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1992/93 (poslední federální liga): mistr HC Sparta Praha — ve finále play-off porazila Vítkovice 3:1. Litvínov byl 1. ZČ, ale vypadl v semifinále. Doloženo webem.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20228,7 +20223,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20240,7 +20235,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20252,7 +20247,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20264,7 +20259,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20276,7 +20271,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20288,7 +20283,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20300,7 +20295,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0042 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK 31 Kežmarok' → 'Kežmarok' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20312,7 +20307,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0042 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20324,7 +20319,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20336,7 +20331,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -20348,7 +20343,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20360,7 +20355,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0078 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -20372,7 +20367,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0078 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20384,7 +20379,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -20396,7 +20391,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0479 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Chirana Piešťany' → 'Chirana Piešťany' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -20408,7 +20403,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: D44 můstek prev_club_id → CLUB_S1991_92_0119 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0479 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -20420,7 +20415,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: D44 můstek prev_club_id → CLUB_S1991_92_0119 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -20432,7 +20427,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0189 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -20444,7 +20439,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0189 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -20456,7 +20451,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -20468,7 +20463,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0211 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -20480,7 +20475,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1991_92_0211 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -20492,7 +20487,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -20504,7 +20499,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -20528,7 +20523,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -20540,7 +20535,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20552,7 +20547,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -20564,7 +20559,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20576,7 +20571,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20588,7 +20583,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20600,7 +20595,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20612,19 +20607,24 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>1992/93 (poslední federální liga): mistr HC Sparta Praha — ve finále play-off porazila Vítkovice 3:1. Litvínov byl 1. ZČ, ale vypadl v semifinále. Doloženo webem.</t>
         </is>
       </c>
     </row>
@@ -26575,6 +26575,9 @@
         <v>5</v>
       </c>
     </row>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
